--- a/docs/chef-menus/loulan/chef-kun-loulan-menus.xlsx
+++ b/docs/chef-menus/loulan/chef-kun-loulan-menus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/doug/culinary-block-collective/docs/chef-menus/loulan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{496FD215-16D1-1A41-B58C-9106B2578BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8FC3547D-BCC8-304B-9F90-5BA747CCF2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11580" yWindow="-18080" windowWidth="20740" windowHeight="16660" xr2:uid="{EBA843FF-26B2-4143-9925-2D46F0982BEA}"/>
   </bookViews>
